--- a/BaoCao/10.TestReport.xlsx
+++ b/BaoCao/10.TestReport.xlsx
@@ -57,7 +57,7 @@
     <t>Pending</t>
   </si>
   <si>
-    <t>Inprogress</t>
+    <t>In progress</t>
   </si>
   <si>
     <t>Blocked</t>
@@ -105,10 +105,10 @@
     <t>Kiểm tra người dùng đăng nhập tài khoản</t>
   </si>
   <si>
-    <t>Đổi  mật khẩu</t>
+    <t>Đổi mật khẩu</t>
   </si>
   <si>
-    <t>Kiểm tra người đổi mật khẩu</t>
+    <t>Kiểm tra người dùng đổi mật khẩu</t>
   </si>
   <si>
     <t>Tài khoản cá nhân</t>
@@ -117,7 +117,7 @@
     <t>Kiểm tra người dùng xem tài khoản cá nhân</t>
   </si>
   <si>
-    <t>Hight</t>
+    <t>High</t>
   </si>
   <si>
     <t>Lấy lại mật khẩu</t>
@@ -129,7 +129,7 @@
     <t>Xem thông tin giáo viên</t>
   </si>
   <si>
-    <t>Kiểm tra người dùng xem thông tin giáo</t>
+    <t>Kiểm tra người dùng xem thông tin giáo viên</t>
   </si>
   <si>
     <t>Tìm kiếm giáo viên</t>
@@ -189,7 +189,7 @@
     <t>Quản lý yêu cầu đặt lịch</t>
   </si>
   <si>
-    <t>Kiểm tra chức năng quản lý yêu cầu đặt hàng</t>
+    <t>Kiểm tra chức năng quản lý yêu cầu đặt lịch</t>
   </si>
   <si>
     <t>Tư vấn trực tuyến</t>
